--- a/ig/DM-37/ValueSet-JDV-ModeleDocumentCDAStructure.xlsx
+++ b/ig/DM-37/ValueSet-JDV-ModeleDocumentCDAStructure.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV-MediaTypeCorpsCDANonStructure</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV-ModeleDocumentCDAStructure</t>
   </si>
   <si>
     <t>Version</t>
